--- a/public/documents/pieces-defense/RF-sur-versement-au-verre.xlsx
+++ b/public/documents/pieces-defense/RF-sur-versement-au-verre.xlsx
@@ -7,8 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Assiette verre-pichet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sur-versement chiffre" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sur-versement par regime" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,216 +466,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sur-versement au verre - depassement de la dose carte</t>
+          <t>Sur-versement au verre - depassement de la dose servie</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Le fisc reconstitue en divisant le volume disponible par la dose EXACTE de la carte. Le free-pour reel depasse cette dose (Kerr 2008 : +23,6 % pour le verre de vin). Le depassement est consomme, jamais vendu.</t>
+          <t>Base = notre mesure de ce qui est reellement servi a la main (hors biere et hors bouteilles). Sans doseur, le free-pour depasse la dose (Kerr 2008 : verre de vin +23,6 %, cocktails +42 %). Le depassement est bu, jamais vendu.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Categorie</t>
+          <t>Poste servi a la main</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Quantite (3 ans)</t>
+          <t>Volume consomme (L)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Volume aux doses carte (L)</t>
+          <t>Taux</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sur-versement (L)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Vin tranquille au verre (15 cl)</t>
+          <t>Vins au verre et au pichet</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>6614</v>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>992</v>
+        <v>3558</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>20 %</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>712</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Vin au pichet (50 / 75 cl)</t>
+          <t>Spiritueux, apéritifs et digestifs au verre</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>2797</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>1432</v>
+        <v>128</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>25 %</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Vin jaune au verre (12 cl)</t>
+          <t>Alcool des cocktails</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>312</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>37</v>
+        <v>789</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>8 %</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>63</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>Vin de paille au verre (6 cl)</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>414</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Cremant au verre (12 cl)</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>814</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL base sur-versable</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="n">
-        <v>10951</v>
-      </c>
-      <c r="C10" s="7" t="n">
-        <v>2567</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Sur-versement au verre - depassement de la dose carte</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Le fisc reconstitue en divisant le volume disponible par la dose EXACTE de la carte. Le free-pour reel depasse cette dose (Kerr 2008 : +23,6 % pour le verre de vin). Le depassement est consomme, jamais vendu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Hypothese de sur-versement</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Taux</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Litres consommes non vendus (3 ans)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Borne basse (prudente)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>15 %</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>RETENU</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>18 %</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Mesure Kerr 2008 (verre de vin)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>23,6 %</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>606</v>
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>4476</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>18,0 %</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>807</v>
       </c>
     </row>
   </sheetData>

--- a/public/documents/pieces-defense/RF-sur-versement-au-verre.xlsx
+++ b/public/documents/pieces-defense/RF-sur-versement-au-verre.xlsx
@@ -514,19 +514,19 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Vins au verre et au pichet</t>
+          <t>Vins tranquilles au verre et au pichet</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>3558</v>
+        <v>3446</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>20 %</t>
+          <t>24 %</t>
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>712</v>
+        <v>813</v>
       </c>
     </row>
     <row r="6">
@@ -540,29 +540,29 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>25 %</t>
+          <t>20 %</t>
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Alcool des cocktails</t>
+          <t>Alcool des cocktails (hors crémant)</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>789</v>
+        <v>517</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>8 %</t>
+          <t>42 %</t>
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>63</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8">
@@ -572,15 +572,15 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>4476</v>
+        <v>4091</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>18,0 %</t>
+          <t>25,8 %</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>807</v>
+        <v>1056</v>
       </c>
     </row>
   </sheetData>

--- a/public/documents/pieces-defense/RF-sur-versement-au-verre.xlsx
+++ b/public/documents/pieces-defense/RF-sur-versement-au-verre.xlsx
@@ -514,11 +514,11 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Vins tranquilles au verre et au pichet</t>
+          <t>Vins au verre et au pichet (y c. vin jaune, paille, macvin)</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>3446</v>
+        <v>3512</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>813</v>
+        <v>829</v>
       </c>
     </row>
     <row r="6">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>128</v>
+        <v>63</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -576,11 +576,11 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>25,8 %</t>
+          <t>25,9 %</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1056</v>
+        <v>1058</v>
       </c>
     </row>
   </sheetData>

--- a/public/documents/pieces-defense/RF-sur-versement-au-verre.xlsx
+++ b/public/documents/pieces-defense/RF-sur-versement-au-verre.xlsx
@@ -7,7 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sur-versement par regime" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Récap par exercice" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Détail 2022-2023" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Détail 2023-2024" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Détail 2024-2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Total 3 exercices" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -469,118 +473,3678 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sur-versement au verre - depassement de la dose servie</t>
+          <t>Sur-versement au verre - consommé + sur-versement, par exercice et par alcool</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Base = notre mesure de ce qui est reellement servi a la main (hors biere et hors bouteilles). Sans doseur, le free-pour depasse la dose (Kerr 2008 : verre de vin +23,6 %, cocktails +42 %). Le depassement est bu, jamais vendu.</t>
+          <t>Base = notre mesure (consoTotaleParBoisson). Taux sources : vin/macvin +23,6 % (Kerr 2008), spiritueux +20 % (Wansink BMJ 2005), cocktails +42 % (Kerr). Crémant et bière traités à part.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Poste servi a la main</t>
+          <t>Exercice</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Volume consomme (L)</t>
+          <t>Consommé (L)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Taux</t>
+          <t>Sur-versement (L)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Sur-versement (L)</t>
+          <t>Total avec sur-versement (L)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Vins au verre et au pichet (y c. vin jaune, paille, macvin)</t>
+          <t>2022-2023</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>3512</v>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>24 %</t>
-        </is>
+        <v>1424.8</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>366.6</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>829</v>
+        <v>1791.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Spiritueux, apéritifs et digestifs au verre</t>
+          <t>2023-2024</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>20 %</t>
-        </is>
+        <v>1363.9</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>353.9</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>13</v>
+        <v>1717.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Alcool des cocktails (hors crémant)</t>
+          <t>2024-2025</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>517</v>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>42 %</t>
-        </is>
+        <v>1302.3</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>337.8</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>217</v>
+        <v>1640.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
+          <t>TOTAL 3 exercices</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>4091.1</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>1058.3</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>5149.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sur-versement au verre - consommé + sur-versement, par exercice et par alcool</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Base = notre mesure (consoTotaleParBoisson). Taux sources : vin/macvin +23,6 % (Kerr 2008), spiritueux +20 % (Wansink BMJ 2005), cocktails +42 % (Kerr). Crémant et bière traités à part.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Alcool</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Consommé (L)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Sur-versement (L)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Total avec sur-versement (L)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Cubis de vin (couleur non précisée)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>92.3</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>483.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Savagnin</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>144.7</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>178.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Trousseau</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>143.4</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>177.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Macvin</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Béthanie</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>123.6</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>152.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Bourgogne Aligoté maison</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>70.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Hautes Côtes de Beaune rouge</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>89.2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Saint Véran</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Saint Joseph Rouge</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>80.59999999999999</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Chablis</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>60.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Moulin à Vent</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>40.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Crème de Cassis</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Rosé Les Jamelles (Clair de Rosé)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>36.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Gewurztraminer</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>33.7</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Bohème Rosé (Le Pive)</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Picon</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Soho Litchi</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Côtes de Provence rosé maison (Cap des Pins)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>8.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Vin Jaune</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Chardonnay</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Liqueur de Cerise</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Vin de Paille</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>9.4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Bordeaux Supérieur</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Vodka</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Miraval Rosé</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Passoa</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Martini Blanc</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Clan Campbell</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Hautes Côtes de Beaune blanc</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Hautes Côtes de Nuits blanc</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Pontarlier Anis</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Tequila Camino Real</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Ricard</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Jack Daniel's</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Pastis 51</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Get 27</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Liqueur de Sapin</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Marc du Jura</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Génépi</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Liqueur de Poire</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Calvados</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Eau de Vie de Poire</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Get 31</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Eau de Vie Framboise</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Cognac</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Bailey's</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Eau de Vie Mirabelle</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Marc de Bourgogne</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="7" t="n">
-        <v>4091</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>25,9 %</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>1058</v>
+      <c r="B54" s="7" t="n">
+        <v>1424.8</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>366.6</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>1791.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D57"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sur-versement au verre - consommé + sur-versement, par exercice et par alcool</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Base = notre mesure (consoTotaleParBoisson). Taux sources : vin/macvin +23,6 % (Kerr 2008), spiritueux +20 % (Wansink BMJ 2005), cocktails +42 % (Kerr). Crémant et bière traités à part.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Alcool</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Consommé (L)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Sur-versement (L)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Total avec sur-versement (L)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Bourgogne Aligoté maison</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>142.8</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>184.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Macvin</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>145.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Côtes de Provence rosé maison (Cap des Pins)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>155.1</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>191.7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Savagnin</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>140.1</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>173.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Côtes du Rhône rouge maison (Chusclan)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>125.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Béthanie</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Trousseau</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>120.3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Saint Véran</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>103.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Macon</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>82.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Hautes Côtes de Beaune rouge</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>65.59999999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Saint Joseph Rouge</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>45.9</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>56.7</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Cubis de vin (couleur non précisée)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Rosé Les Jamelles (Clair de Rosé)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>43.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Moulin à Vent</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>42.6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Crème de Cassis</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Gewurztraminer</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Picon</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Chablis</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>18.4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Soho Litchi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Vin Jaune</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Chardonnay</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Liqueur de Cerise</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Rosé Le Pive</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Côtes de Provence Rosé Minuty</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Vin de Paille</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Vodka</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Passoa</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Grand Pavois</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Martini Blanc</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Pontarlier Anis</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Clan Campbell</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Liqueur de Sapin</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Hautes Côtes de Beaune blanc</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Ricard</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Pastis 51</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Get 27</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Jack Daniel's</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Génépi</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Bailey's</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Marc du Jura</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Grand Marnier</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Eau de Vie Mirabelle</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Eau de Vie de Poire</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Cognac</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Calvados</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Liqueur de Poire</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Get 31</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Eau de Vie Framboise</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Tequila Camino Real</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Marc de Bourgogne</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Guignolet</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>1363.9</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>353.9</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>1717.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D53"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sur-versement au verre - consommé + sur-versement, par exercice et par alcool</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Base = notre mesure (consoTotaleParBoisson). Taux sources : vin/macvin +23,6 % (Kerr 2008), spiritueux +20 % (Wansink BMJ 2005), cocktails +42 % (Kerr). Crémant et bière traités à part.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Alcool</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Consommé (L)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Sur-versement (L)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Total avec sur-versement (L)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Bourgogne Aligoté maison</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>154.5</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>199.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Macvin</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>135.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Savagnin</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>144.7</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>178.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Côtes de Provence rosé maison (Cap des Pins)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>125.8</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>155.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Trousseau</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>130.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Saint Véran</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>110.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Côtes du Rhône rouge maison (Chusclan)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>110.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Béthanie</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>109.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Macon</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Saint Joseph Rouge</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>66.90000000000001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Hautes Côtes de Beaune rouge</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>46.8</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>57.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Moulin à Vent</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Rosé Les Jamelles (Clair de Rosé)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Crème de Cassis</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>23.4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Gewurztraminer</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Picon</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>13.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Rosé Le Pive</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>20.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Soho Litchi</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Vin Jaune</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Chardonnay</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Chablis</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Liqueur de Cerise</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Vin de Paille</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Passoa</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Vodka</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Grand Pavois</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Martini Blanc</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Côtes de Provence Rosé Minuty</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Pontarlier Anis</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Clan Campbell</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Ricard</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Liqueur de Sapin</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Pastis 51</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Génépi</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Eau de Vie de Poire</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Get 27</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Marc du Jura</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Calvados</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Liqueur de Poire</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Jack Daniel's</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Eau de Vie Mirabelle</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Bailey's</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Cognac</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Grand Marnier</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Eau de Vie Framboise</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Marc de Bourgogne</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Get 31</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>1302.3</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>337.8</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>1640.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Sur-versement au verre - consommé + sur-versement, par exercice et par alcool</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Base = notre mesure (consoTotaleParBoisson). Taux sources : vin/macvin +23,6 % (Kerr 2008), spiritueux +20 % (Wansink BMJ 2005), cocktails +42 % (Kerr). Crémant et bière traités à part.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Alcool</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Consommé (L)</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Sur-versement (L)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Total avec sur-versement (L)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Macvin</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>293.3</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>404.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Bourgogne Aligoté maison</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>346.8</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Savagnin</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>429.5</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>530.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Cubis de vin (couleur non précisée)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>426.9</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>527.6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Trousseau</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>346.1</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>81.7</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>427.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Béthanie</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>309.9</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>383.1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Côtes de Provence rosé maison (Cap des Pins)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>286.8</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>355.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Saint Véran</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>245.4</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>57.9</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>303.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Côtes du Rhône rouge maison (Chusclan)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>190.8</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>235.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Hautes Côtes de Beaune rouge</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>172.1</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>40.6</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>212.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Saint Joseph Rouge</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>165.2</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>204.1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Macon</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>139.8</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>172.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Moulin à Vent</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>128.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Rosé Les Jamelles (Clair de Rosé)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Crème de Cassis</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>71.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Gewurztraminer</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>97.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Chablis</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>91.09999999999999</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Picon</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>40.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Soho Litchi</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>33.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Vin Jaune</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>46.3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Arbois Chardonnay</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>40.3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Liqueur de Cerise</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>22.8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Rosé Le Pive</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Vin de Paille</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>Vodka</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Passoa</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Bohème Rosé (Le Pive)</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Côtes de Provence Rosé Minuty</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>13.9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Martini Blanc</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>15.1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Grand Pavois</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Clan Campbell</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Pontarlier Anis</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Bordeaux Supérieur</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>8.300000000000001</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Porto</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Miraval Rosé</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Hautes Côtes de Beaune blanc</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Ricard</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Liqueur de Sapin</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Pastis 51</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Get 27</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Jack Daniel's</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Hautes Côtes de Nuits blanc</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Tequila Camino Real</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Marc du Jura</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>Génépi</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Eau de Vie de Poire</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>Calvados</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Liqueur de Poire</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>Bailey's</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Eau de Vie Mirabelle</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>Cognac</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>Get 31</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>Eau de Vie Framboise</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Grand Marnier</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Marc de Bourgogne</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Guignolet</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="n">
+        <v>4091.1</v>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>1058.3</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>5149.4</v>
       </c>
     </row>
   </sheetData>

--- a/public/documents/pieces-defense/RF-sur-versement-au-verre.xlsx
+++ b/public/documents/pieces-defense/RF-sur-versement-au-verre.xlsx
@@ -525,10 +525,10 @@
         <v>1424.8</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>366.6</v>
+        <v>247.7</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1791.5</v>
+        <v>1672.5</v>
       </c>
     </row>
     <row r="6">
@@ -541,10 +541,10 @@
         <v>1363.9</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>353.9</v>
+        <v>236.7</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1717.8</v>
+        <v>1600.7</v>
       </c>
     </row>
     <row r="7">
@@ -557,10 +557,10 @@
         <v>1302.3</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>337.8</v>
+        <v>236.1</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1640.1</v>
+        <v>1538.4</v>
       </c>
     </row>
     <row r="8">
@@ -573,10 +573,10 @@
         <v>4091.1</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>1058.3</v>
+        <v>720.5</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>5149.4</v>
+        <v>4811.5</v>
       </c>
     </row>
   </sheetData>
@@ -638,145 +638,145 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Cubis de vin (couleur non précisée)</t>
+          <t>Macvin</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>391.3</v>
+        <v>89.7</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>92.3</v>
+        <v>33.8</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>483.6</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Arbois Savagnin</t>
+          <t>Arbois Béthanie</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>144.7</v>
+        <v>123.6</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>34.2</v>
+        <v>29.2</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>178.9</v>
+        <v>152.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Arbois Trousseau</t>
+          <t>Arbois Savagnin</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>143.4</v>
+        <v>144.7</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>33.8</v>
+        <v>25.5</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>177.3</v>
+        <v>170.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Macvin</t>
+          <t>Arbois Trousseau</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>89.7</v>
+        <v>143.4</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>33.8</v>
+        <v>22.6</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>123.5</v>
+        <v>166.1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Arbois Béthanie</t>
+          <t>Bourgogne Aligoté maison</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>123.6</v>
+        <v>49.5</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>29.2</v>
+        <v>20.8</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>152.7</v>
+        <v>70.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Bourgogne Aligoté maison</t>
+          <t>Hautes Côtes de Beaune rouge</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>49.5</v>
+        <v>72.2</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>20.8</v>
+        <v>14</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>70.3</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Hautes Côtes de Beaune rouge</t>
+          <t>Saint Véran</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>72.2</v>
+        <v>72</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>17</v>
+        <v>13.7</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>89.2</v>
+        <v>85.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Saint Véran</t>
+          <t>Saint Joseph Rouge</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>72</v>
+        <v>65.2</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>89</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Saint Joseph Rouge</t>
+          <t>Cubis de vin (couleur non précisée)</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>65.2</v>
+        <v>391.3</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>15.4</v>
+        <v>11</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>80.59999999999999</v>
+        <v>402.3</v>
       </c>
     </row>
     <row r="14">
@@ -789,74 +789,74 @@
         <v>49.1</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>11.6</v>
+        <v>8.6</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>60.7</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Moulin à Vent</t>
+          <t>Crème de Cassis</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>32.9</v>
+        <v>16.8</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>40.7</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Crème de Cassis</t>
+          <t>Rosé Les Jamelles (Clair de Rosé)</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>16.8</v>
+        <v>29.2</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>23.8</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Rosé Les Jamelles (Clair de Rosé)</t>
+          <t>Gewurztraminer</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>29.2</v>
+        <v>27.2</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>6.9</v>
+        <v>5.1</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>36.2</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Gewurztraminer</t>
+          <t>Moulin à Vent</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>27.2</v>
+        <v>32.9</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>33.7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19">
@@ -1086,27 +1086,27 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Hautes Côtes de Beaune blanc</t>
+          <t>Hautes Côtes de Nuits blanc</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Hautes Côtes de Nuits blanc</t>
+          <t>Pontarlier Anis</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="C34" s="5" t="n">
         <v>0.5</v>
@@ -1118,39 +1118,39 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Pontarlier Anis</t>
+          <t>Tequila Camino Real</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="C35" s="5" t="n">
         <v>0.5</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Tequila Camino Real</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Ricard</t>
         </is>
       </c>
       <c r="B37" s="5" t="n">
@@ -1160,29 +1160,29 @@
         <v>0.4</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Ricard</t>
+          <t>Jack Daniel's</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Jack Daniel's</t>
+          <t>Pastis 51</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
@@ -1198,71 +1198,71 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Pastis 51</t>
+          <t>Get 27</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="C40" s="5" t="n">
         <v>0.3</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Get 27</t>
+          <t>Liqueur de Sapin</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Liqueur de Sapin</t>
+          <t>Marc du Jura</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="C42" s="5" t="n">
         <v>0.2</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Marc du Jura</t>
+          <t>Génépi</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Génépi</t>
+          <t>Liqueur de Poire</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
@@ -1278,23 +1278,23 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Liqueur de Poire</t>
+          <t>Calvados</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C45" s="5" t="n">
         <v>0.1</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Calvados</t>
+          <t>Eau de Vie de Poire</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
@@ -1310,7 +1310,7 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Eau de Vie de Poire</t>
+          <t>Get 31</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
@@ -1326,55 +1326,55 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Get 31</t>
+          <t>Eau de Vie Framboise</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C48" s="5" t="n">
         <v>0.1</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Eau de Vie Framboise</t>
+          <t>Cognac</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C49" s="5" t="n">
         <v>0.1</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Cognac</t>
+          <t>Bailey's</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Bailey's</t>
+          <t>Eau de Vie Mirabelle</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
@@ -1390,33 +1390,33 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Eau de Vie Mirabelle</t>
+          <t>Marc de Bourgogne</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Marc de Bourgogne</t>
+          <t>Hautes Côtes de Beaune blanc</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="C53" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -1429,10 +1429,10 @@
         <v>1424.8</v>
       </c>
       <c r="C54" s="7" t="n">
-        <v>366.6</v>
+        <v>247.7</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>1791.5</v>
+        <v>1672.5</v>
       </c>
     </row>
   </sheetData>
@@ -1494,49 +1494,49 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Bourgogne Aligoté maison</t>
+          <t>Macvin</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>142.8</v>
+        <v>105.5</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>41.7</v>
+        <v>40.2</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>184.5</v>
+        <v>145.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Macvin</t>
+          <t>Bourgogne Aligoté maison</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>105.5</v>
+        <v>142.8</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>40.2</v>
+        <v>24</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>145.7</v>
+        <v>166.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Côtes de Provence rosé maison (Cap des Pins)</t>
+          <t>Arbois Béthanie</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>155.1</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>36.7</v>
+        <v>23.1</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>191.7</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8">
@@ -1549,218 +1549,218 @@
         <v>140.1</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>33.1</v>
+        <v>22.9</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>173.1</v>
+        <v>163</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Côtes du Rhône rouge maison (Chusclan)</t>
+          <t>Saint Véran</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>101.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>24</v>
+        <v>15.9</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>125.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Arbois Béthanie</t>
+          <t>Arbois Trousseau</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>97.90000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>23.1</v>
+        <v>13.4</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>121</v>
+        <v>110.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Arbois Trousseau</t>
+          <t>Macon</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>97.3</v>
+        <v>67</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>23</v>
+        <v>10.3</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>120.3</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Saint Véran</t>
+          <t>Hautes Côtes de Beaune rouge</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>84.09999999999999</v>
+        <v>53.1</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>19.8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>103.9</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Macon</t>
+          <t>Rosé Les Jamelles (Clair de Rosé)</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>67</v>
+        <v>34.9</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>15.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>82.8</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Hautes Côtes de Beaune rouge</t>
+          <t>Saint Joseph Rouge</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>53.1</v>
+        <v>45.9</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>65.59999999999999</v>
+        <v>53.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Saint Joseph Rouge</t>
+          <t>Crème de Cassis</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>45.9</v>
+        <v>17.2</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>10.8</v>
+        <v>7.2</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>56.7</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Cubis de vin (couleur non précisée)</t>
+          <t>Côtes de Provence rosé maison (Cap des Pins)</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>35.6</v>
+        <v>155.1</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>8.4</v>
+        <v>6.5</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>44</v>
+        <v>161.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Rosé Les Jamelles (Clair de Rosé)</t>
+          <t>Gewurztraminer</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>34.9</v>
+        <v>24.9</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>43.1</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Moulin à Vent</t>
+          <t>Picon</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>34.5</v>
+        <v>10.5</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>8.1</v>
+        <v>4.4</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>42.6</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Crème de Cassis</t>
+          <t>Côtes du Rhône rouge maison (Chusclan)</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>17.2</v>
+        <v>101.5</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>24.4</v>
+        <v>105.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Gewurztraminer</t>
+          <t>Moulin à Vent</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>24.9</v>
+        <v>34.5</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>30.8</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Picon</t>
+          <t>Soho Litchi</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>14.9</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="22">
@@ -1773,234 +1773,234 @@
         <v>14.8</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Soho Litchi</t>
+          <t>Arbois Vin Jaune</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>8.199999999999999</v>
+        <v>12.2</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>11.6</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Arbois Vin Jaune</t>
+          <t>Arbois Chardonnay</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>12.2</v>
+        <v>10.3</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>15.1</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Arbois Chardonnay</t>
+          <t>Liqueur de Cerise</t>
         </is>
       </c>
       <c r="B25" s="5" t="n">
-        <v>10.3</v>
+        <v>5.6</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>12.7</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Liqueur de Cerise</t>
+          <t>Rosé Le Pive</t>
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>5.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C26" s="5" t="n">
         <v>2.3</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>7.9</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Rosé Le Pive</t>
+          <t>Côtes de Provence Rosé Minuty</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>12.1</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Côtes de Provence Rosé Minuty</t>
+          <t>Vin de Paille</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Vin de Paille</t>
+          <t>Vodka</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>8.1</v>
+        <v>4.1</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>10</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Vodka</t>
+          <t>Passoa</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Passoa</t>
+          <t>Grand Pavois</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Grand Pavois</t>
+          <t>Martini Blanc</t>
         </is>
       </c>
       <c r="B32" s="5" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>6.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Martini Blanc</t>
+          <t>Pontarlier Anis</t>
         </is>
       </c>
       <c r="B33" s="5" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Pontarlier Anis</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="B34" s="5" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="C34" s="5" t="n">
         <v>0.6</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Clan Campbell</t>
         </is>
       </c>
       <c r="B35" s="5" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="C35" s="5" t="n">
         <v>0.6</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Clan Campbell</t>
+          <t>Cubis de vin (couleur non précisée)</t>
         </is>
       </c>
       <c r="B36" s="5" t="n">
-        <v>1.8</v>
+        <v>35.6</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>2.4</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="37">
@@ -2022,135 +2022,135 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Hautes Côtes de Beaune blanc</t>
+          <t>Ricard</t>
         </is>
       </c>
       <c r="B38" s="5" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Ricard</t>
+          <t>Pastis 51</t>
         </is>
       </c>
       <c r="B39" s="5" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="C39" s="5" t="n">
         <v>0.3</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Pastis 51</t>
+          <t>Get 27</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Get 27</t>
+          <t>Jack Daniel's</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="C41" s="5" t="n">
         <v>0.2</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Jack Daniel's</t>
+          <t>Génépi</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="C42" s="5" t="n">
         <v>0.2</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Génépi</t>
+          <t>Bailey's</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="C43" s="5" t="n">
         <v>0.2</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Bailey's</t>
+          <t>Marc du Jura</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D44" s="5" t="n">
         <v>0.8</v>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D44" s="5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Marc du Jura</t>
+          <t>Grand Marnier</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="C45" s="5" t="n">
         <v>0.1</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Grand Marnier</t>
+          <t>Eau de Vie Mirabelle</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
@@ -2166,23 +2166,23 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Eau de Vie Mirabelle</t>
+          <t>Eau de Vie de Poire</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="C47" s="5" t="n">
         <v>0.1</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Eau de Vie de Poire</t>
+          <t>Cognac</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
@@ -2198,7 +2198,7 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Cognac</t>
+          <t>Calvados</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
@@ -2208,13 +2208,13 @@
         <v>0.1</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Calvados</t>
+          <t>Liqueur de Poire</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
@@ -2230,7 +2230,7 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Liqueur de Poire</t>
+          <t>Get 31</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
@@ -2246,55 +2246,55 @@
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Get 31</t>
+          <t>Eau de Vie Framboise</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C52" s="5" t="n">
         <v>0.1</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Eau de Vie Framboise</t>
+          <t>Tequila Camino Real</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Tequila Camino Real</t>
+          <t>Marc de Bourgogne</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Marc de Bourgogne</t>
+          <t>Guignolet</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
@@ -2310,17 +2310,17 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Guignolet</t>
+          <t>Hautes Côtes de Beaune blanc</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="C56" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="57">
@@ -2333,10 +2333,10 @@
         <v>1363.9</v>
       </c>
       <c r="C57" s="7" t="n">
-        <v>353.9</v>
+        <v>236.7</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>1717.8</v>
+        <v>1600.7</v>
       </c>
     </row>
   </sheetData>
@@ -2398,33 +2398,33 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Bourgogne Aligoté maison</t>
+          <t>Macvin</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>154.5</v>
+        <v>98</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>44.7</v>
+        <v>37.2</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>199.2</v>
+        <v>135.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Macvin</t>
+          <t>Bourgogne Aligoté maison</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>98</v>
+        <v>154.5</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>37.2</v>
+        <v>25.2</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>135.2</v>
+        <v>179.7</v>
       </c>
     </row>
     <row r="7">
@@ -2437,26 +2437,26 @@
         <v>144.7</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>34.1</v>
+        <v>22.9</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>178.8</v>
+        <v>167.6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Côtes de Provence rosé maison (Cap des Pins)</t>
+          <t>Arbois Béthanie</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>125.8</v>
+        <v>88.5</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>29.7</v>
+        <v>20.9</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>155.5</v>
+        <v>109.4</v>
       </c>
     </row>
     <row r="9">
@@ -2469,10 +2469,10 @@
         <v>105.3</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>24.9</v>
+        <v>16</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>130.2</v>
+        <v>121.3</v>
       </c>
     </row>
     <row r="10">
@@ -2485,186 +2485,186 @@
         <v>89.40000000000001</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>21.1</v>
+        <v>15.3</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>110.5</v>
+        <v>104.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Côtes du Rhône rouge maison (Chusclan)</t>
+          <t>Macon</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>89.3</v>
+        <v>72.8</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>21.1</v>
+        <v>12</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>110.4</v>
+        <v>84.90000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Arbois Béthanie</t>
+          <t>Saint Joseph Rouge</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>88.5</v>
+        <v>54.1</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>20.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>109.4</v>
+        <v>63.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Macon</t>
+          <t>Rosé Les Jamelles (Clair de Rosé)</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>72.8</v>
+        <v>33.8</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>17.2</v>
+        <v>8</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>90</v>
+        <v>41.7</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Saint Joseph Rouge</t>
+          <t>Hautes Côtes de Beaune rouge</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>54.1</v>
+        <v>46.8</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>12.8</v>
+        <v>7.6</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>66.90000000000001</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Hautes Côtes de Beaune rouge</t>
+          <t>Côtes de Provence rosé maison (Cap des Pins)</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>46.8</v>
+        <v>125.8</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>11.1</v>
+        <v>7</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>57.9</v>
+        <v>132.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Moulin à Vent</t>
+          <t>Crème de Cassis</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>36.4</v>
+        <v>16.4</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>8.6</v>
+        <v>6.9</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>45</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Rosé Les Jamelles (Clair de Rosé)</t>
+          <t>Gewurztraminer</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>33.8</v>
+        <v>26.8</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>41.7</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Crème de Cassis</t>
+          <t>Moulin à Vent</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>16.4</v>
+        <v>36.4</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>6.9</v>
+        <v>5.2</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>23.4</v>
+        <v>41.6</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Gewurztraminer</t>
+          <t>Picon</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>26.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>6.3</v>
+        <v>4.1</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>33.1</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Picon</t>
+          <t>Rosé Le Pive</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>9.699999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>13.7</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Rosé Le Pive</t>
+          <t>Côtes du Rhône rouge maison (Chusclan)</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>16.5</v>
+        <v>89.3</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>20.4</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -3173,10 +3173,10 @@
         <v>1302.3</v>
       </c>
       <c r="C53" s="7" t="n">
-        <v>337.8</v>
+        <v>236.1</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>1640.1</v>
+        <v>1538.4</v>
       </c>
     </row>
   </sheetData>
@@ -3254,17 +3254,17 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Bourgogne Aligoté maison</t>
+          <t>Arbois Béthanie</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>346.8</v>
+        <v>309.9</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>107.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>454</v>
+        <v>383.1</v>
       </c>
     </row>
     <row r="7">
@@ -3277,26 +3277,26 @@
         <v>429.5</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>101.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>530.8</v>
+        <v>500.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Cubis de vin (couleur non précisée)</t>
+          <t>Bourgogne Aligoté maison</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>426.9</v>
+        <v>346.8</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>100.7</v>
+        <v>70</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>527.6</v>
+        <v>416.8</v>
       </c>
     </row>
     <row r="9">
@@ -3309,250 +3309,250 @@
         <v>346.1</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>81.7</v>
+        <v>52.1</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>427.8</v>
+        <v>398.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Arbois Béthanie</t>
+          <t>Saint Véran</t>
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>309.9</v>
+        <v>245.4</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>73.09999999999999</v>
+        <v>44.9</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>383.1</v>
+        <v>290.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Côtes de Provence rosé maison (Cap des Pins)</t>
+          <t>Hautes Côtes de Beaune rouge</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>286.8</v>
+        <v>172.1</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>68.90000000000001</v>
+        <v>30.6</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>355.6</v>
+        <v>202.7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Saint Véran</t>
+          <t>Saint Joseph Rouge</t>
         </is>
       </c>
       <c r="B12" s="5" t="n">
-        <v>245.4</v>
+        <v>165.2</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>57.9</v>
+        <v>29.4</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>303.4</v>
+        <v>194.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Côtes du Rhône rouge maison (Chusclan)</t>
+          <t>Rosé Les Jamelles (Clair de Rosé)</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>190.8</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>45</v>
+        <v>23.1</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>235.8</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Hautes Côtes de Beaune rouge</t>
+          <t>Macon</t>
         </is>
       </c>
       <c r="B14" s="5" t="n">
-        <v>172.1</v>
+        <v>139.8</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>40.6</v>
+        <v>22.3</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>212.7</v>
+        <v>162.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Saint Joseph Rouge</t>
+          <t>Crème de Cassis</t>
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>165.2</v>
+        <v>50.4</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>39</v>
+        <v>21.2</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>204.1</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Macon</t>
+          <t>Côtes de Provence rosé maison (Cap des Pins)</t>
         </is>
       </c>
       <c r="B16" s="5" t="n">
-        <v>139.8</v>
+        <v>286.8</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>33</v>
+        <v>15.9</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>172.8</v>
+        <v>302.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Moulin à Vent</t>
+          <t>Gewurztraminer</t>
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>103.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>24.5</v>
+        <v>15.7</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>128.2</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Rosé Les Jamelles (Clair de Rosé)</t>
+          <t>Chablis</t>
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>97.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>23.1</v>
+        <v>14.1</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>121</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Crème de Cassis</t>
+          <t>Moulin à Vent</t>
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>50.4</v>
+        <v>103.8</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>21.2</v>
+        <v>13.3</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>71.5</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Gewurztraminer</t>
+          <t>Picon</t>
         </is>
       </c>
       <c r="B20" s="5" t="n">
-        <v>78.90000000000001</v>
+        <v>28.3</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>18.6</v>
+        <v>11.9</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>97.5</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Chablis</t>
+          <t>Cubis de vin (couleur non précisée)</t>
         </is>
       </c>
       <c r="B21" s="5" t="n">
-        <v>73.7</v>
+        <v>426.9</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>17.4</v>
+        <v>11.5</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>91.09999999999999</v>
+        <v>438.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Picon</t>
+          <t>Soho Litchi</t>
         </is>
       </c>
       <c r="B22" s="5" t="n">
-        <v>28.3</v>
+        <v>23.3</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>11.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>40.2</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Soho Litchi</t>
+          <t>Arbois Vin Jaune</t>
         </is>
       </c>
       <c r="B23" s="5" t="n">
-        <v>23.3</v>
+        <v>37.4</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>33.1</v>
+        <v>46.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Arbois Vin Jaune</t>
+          <t>Côtes du Rhône rouge maison (Chusclan)</t>
         </is>
       </c>
       <c r="B24" s="5" t="n">
-        <v>37.4</v>
+        <v>190.8</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>46.3</v>
+        <v>198.7</v>
       </c>
     </row>
     <row r="25">
@@ -3798,183 +3798,183 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Hautes Côtes de Beaune blanc</t>
+          <t>Ricard</t>
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Ricard</t>
+          <t>Liqueur de Sapin</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>6.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Liqueur de Sapin</t>
+          <t>Pastis 51</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="C42" s="5" t="n">
         <v>0.9</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>Pastis 51</t>
+          <t>Get 27</t>
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Get 27</t>
+          <t>Jack Daniel's</t>
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Jack Daniel's</t>
+          <t>Hautes Côtes de Nuits blanc</t>
         </is>
       </c>
       <c r="B45" s="5" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Hautes Côtes de Nuits blanc</t>
+          <t>Tequila Camino Real</t>
         </is>
       </c>
       <c r="B46" s="5" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="C46" s="5" t="n">
         <v>0.5</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>Tequila Camino Real</t>
+          <t>Marc du Jura</t>
         </is>
       </c>
       <c r="B47" s="5" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="C47" s="5" t="n">
         <v>0.5</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>Marc du Jura</t>
+          <t>Génépi</t>
         </is>
       </c>
       <c r="B48" s="5" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="C48" s="5" t="n">
         <v>0.5</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Génépi</t>
+          <t>Eau de Vie de Poire</t>
         </is>
       </c>
       <c r="B49" s="5" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Eau de Vie de Poire</t>
+          <t>Calvados</t>
         </is>
       </c>
       <c r="B50" s="5" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="C50" s="5" t="n">
         <v>0.3</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Calvados</t>
+          <t>Liqueur de Poire</t>
         </is>
       </c>
       <c r="B51" s="5" t="n">
@@ -3984,17 +3984,17 @@
         <v>0.3</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Liqueur de Poire</t>
+          <t>Bailey's</t>
         </is>
       </c>
       <c r="B52" s="5" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="C52" s="5" t="n">
         <v>0.3</v>
@@ -4006,39 +4006,39 @@
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>Bailey's</t>
+          <t>Eau de Vie Mirabelle</t>
         </is>
       </c>
       <c r="B53" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D53" s="5" t="n">
         <v>1.3</v>
-      </c>
-      <c r="C53" s="5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>1.6</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>Eau de Vie Mirabelle</t>
+          <t>Cognac</t>
         </is>
       </c>
       <c r="B54" s="5" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="C54" s="5" t="n">
         <v>0.2</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Cognac</t>
+          <t>Get 31</t>
         </is>
       </c>
       <c r="B55" s="5" t="n">
@@ -4054,81 +4054,81 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Get 31</t>
+          <t>Eau de Vie Framboise</t>
         </is>
       </c>
       <c r="B56" s="5" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="C56" s="5" t="n">
         <v>0.2</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
         <is>
-          <t>Eau de Vie Framboise</t>
+          <t>Grand Marnier</t>
         </is>
       </c>
       <c r="B57" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D57" s="5" t="n">
         <v>0.8</v>
-      </c>
-      <c r="C57" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D57" s="5" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>Grand Marnier</t>
+          <t>Marc de Bourgogne</t>
         </is>
       </c>
       <c r="B58" s="5" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Marc de Bourgogne</t>
+          <t>Guignolet</t>
         </is>
       </c>
       <c r="B59" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C59" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Guignolet</t>
+          <t>Hautes Côtes de Beaune blanc</t>
         </is>
       </c>
       <c r="B60" s="5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="C60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="61">
@@ -4141,10 +4141,10 @@
         <v>4091.1</v>
       </c>
       <c r="C61" s="7" t="n">
-        <v>1058.3</v>
+        <v>720.5</v>
       </c>
       <c r="D61" s="7" t="n">
-        <v>5149.4</v>
+        <v>4811.5</v>
       </c>
     </row>
   </sheetData>
